--- a/data/Availability Calendar(1).xlsx
+++ b/data/Availability Calendar(1).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MGR-TANTAWY\Desktop\STOP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69E73C1C-74E8-4F38-B7F1-0EAA0547C079}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{491CFE64-2CD8-452F-8481-5760BF97AD8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="28" activeTab="28" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="28" activeTab="29" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="July" sheetId="8" state="hidden" r:id="rId1"/>
@@ -56024,10 +56024,10 @@
       <c r="V10" s="7"/>
       <c r="W10" s="7"/>
       <c r="X10" s="7"/>
-      <c r="Y10" s="23"/>
-      <c r="Z10" s="23"/>
+      <c r="Y10" s="7"/>
+      <c r="Z10" s="7"/>
       <c r="AA10" s="23"/>
-      <c r="AB10" s="23"/>
+      <c r="AB10" s="7"/>
       <c r="AC10" s="7"/>
       <c r="AD10" s="7"/>
       <c r="AE10" s="7"/>
